--- a/results/emp008_runs/origin_emp008/comparison/active_weight_sum.xlsx
+++ b/results/emp008_runs/origin_emp008/comparison/active_weight_sum.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,6 +1158,23 @@
         <v>6.165569602969297</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0.1358875526054735</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.06794377630273676</v>
+      </c>
+      <c r="D43" t="n">
+        <v>13.58875526054735</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6.794377630273677</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
